--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D15B55-5009-40E8-AAB3-B5FA5FCB16CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
     <sheet name="第二個說明對話" sheetId="2" r:id="rId2"/>
+    <sheet name="第三個說明對話" sheetId="3" r:id="rId3"/>
+    <sheet name="第四個說明對話" sheetId="4" r:id="rId4"/>
+    <sheet name="第五個說明對話" sheetId="5" r:id="rId5"/>
+    <sheet name="第六個說明對話" sheetId="6" r:id="rId6"/>
+    <sheet name="第七個說明對話" sheetId="7" r:id="rId7"/>
+    <sheet name="第八個說明對話" sheetId="9" r:id="rId8"/>
+    <sheet name="第九個說明對話" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="32">
   <si>
     <t>對話內容</t>
   </si>
@@ -53,34 +59,117 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>我是對話內容第2句話</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是對話內容第3句話</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是對話內容第1句話</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是對話內容第11句話</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是對話內容第22句話</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我是對話內容第33句話</t>
+    <t>克拉拉Klarra</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉Klarra</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉Klarra</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>聽起來那些"老主顧"又回來了，你覺得牠們很討厭？等你見到其他"老主顧"就會覺得牠們可愛了。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這就完了？通訊器恢復正常只有一天，昨天成功連絡上我們的也只有那兩位，今天陸陸續續有其他人也成功恢復通訊了，明天有得忙的。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">把它拿進來，先用&lt;color=#FFBB77&gt;開殼機&lt;/color&gt;打開，從內部構造才能看出是犯了什麼毛病
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#FFBB77&gt;損壞核心&lt;/color&gt;，修好它是這間工作室存在的意義
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你把損壞核心交給&lt;color=#FFBB77&gt;開殼機&lt;/color&gt;，它會自動幫你完成作業，&lt;color=#FFBB77&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;，建議你再忙都要注意耐久值的狀況。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">現在把核心拿到&lt;color=#FFBB77&gt;工作台&lt;/color&gt;上，這樣能看得更清楚
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">這樣清楚多了，你得透過&lt;color=#FFBB77&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;，可處理的&lt;color=#FFBB77&gt;零件有三樣，處理器、電路板和原液&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你成功修好過通訊器，修復這個對你應該沒什麼難的，看到&lt;color=#FFBB77&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯毛病出在它身上，&lt;color=#FFBB77&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">就是這樣，這下核心的修復已經完成，把它&lt;color=#FFBB77&gt;還給顧客&lt;/color&gt;吧，記得客氣一點，他算是有耐心的一位了
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每個人的&lt;color=#FFBB77&gt;耐心是有限的&lt;/color&gt;，你必須在顧客能等待的時間內交予修好的核心，否則&lt;color=#FFBB77&gt;時間一到他就會直接離開&lt;/color&gt;，咱們也拿不到報酬了，</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你能透過顧客身邊的&lt;color=#FFBB77&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你，你賺到你在這裡的第一筆&lt;color=#FFBB77&gt;報酬&lt;/color&gt;了，接著準備下一單吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">貨幣已經被克拉拉姐姐收走了，&lt;color=#FFBB77&gt;貨幣會被換算成績分，你可以透過計分器看到累積了多少報酬，顧客付款時剩餘的耐心值越高，收到的貨幣也越多&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">這次需要更換的是&lt;color=#FFBB77&gt;原液&lt;/color&gt;，&lt;color=#FFBB77&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你看到四種不同的原料了嗎？&lt;color=#FFBB77&gt;根據顏色放入注射器，它會為你產出相應的原液&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒錯，&lt;color=#FFBB77&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#FFBB77&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉打擾你們......但是有隻&lt;color=#FFBB77&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#FFBB77&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸好牠的個子小，膽子也不大，&lt;color=#FFBB77&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">要聊等關門後再說，&lt;color=#FFBB77&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=#FFBB77&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#FFBB77&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
+</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -667,9 +756,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1025,17 +1117,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1052,15 +1144,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1069,37 +1161,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1111,14 +1186,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB011BD-DBB0-4E2C-AD35-6A2E6D905887}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="39.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1135,15 +1211,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="99" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1152,37 +1228,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1191,4 +1250,516 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="132" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="45.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="36.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="47.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="40.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -79,89 +79,89 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">把它拿進來，先用&lt;color=#FFBB77&gt;開殼機&lt;/color&gt;打開，從內部構造才能看出是犯了什麼毛病
+    <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#A23400&gt;損壞核心&lt;/color&gt;，修好它是這間工作室存在的意義
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#FFBB77&gt;損壞核心&lt;/color&gt;，修好它是這間工作室存在的意義
+    <t xml:space="preserve">把它拿進來，先用&lt;color=#A23400&gt;開殼機&lt;/color&gt;打開，從內部構造才能看出是犯了什麼毛病
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>你把損壞核心交給&lt;color=#FFBB77&gt;開殼機&lt;/color&gt;，它會自動幫你完成作業，&lt;color=#FFBB77&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;，建議你再忙都要注意耐久值的狀況。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">現在把核心拿到&lt;color=#FFBB77&gt;工作台&lt;/color&gt;上，這樣能看得更清楚
+    <t>抱歉打擾你們......但是有隻&lt;color=color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=color=#A23400&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸好牠的個子小，膽子也不大，&lt;color=color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">這樣清楚多了，你得透過&lt;color=#FFBB77&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;，可處理的&lt;color=#FFBB77&gt;零件有三樣，處理器、電路板和原液&lt;/color&gt;。
+    <t>你把損壞核心交給&lt;color=#A23400&gt;開殼機&lt;/color&gt;，它會自動幫你完成作業，&lt;color=#A23400&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;，建議你再忙都要注意耐久值的狀況。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">現在把核心拿到&lt;color=#A23400&gt;工作台&lt;/color&gt;上，這樣能看得更清楚
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">你成功修好過通訊器，修復這個對你應該沒什麼難的，看到&lt;color=#FFBB77&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯毛病出在它身上，&lt;color=#FFBB77&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。
+    <t xml:space="preserve">這樣清楚多了，你得透過&lt;color=#A23400&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;，可處理的&lt;color=#A23400&gt;零件有三樣，處理器、電路板和原液&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">就是這樣，這下核心的修復已經完成，把它&lt;color=#FFBB77&gt;還給顧客&lt;/color&gt;吧，記得客氣一點，他算是有耐心的一位了
+    <t xml:space="preserve">你成功修好過通訊器，修復這個對你應該沒什麼難的，看到&lt;color=#A23400&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯毛病出在它身上，&lt;color=#A23400&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>每個人的&lt;color=#FFBB77&gt;耐心是有限的&lt;/color&gt;，你必須在顧客能等待的時間內交予修好的核心，否則&lt;color=#FFBB77&gt;時間一到他就會直接離開&lt;/color&gt;，咱們也拿不到報酬了，</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你能透過顧客身邊的&lt;color=#FFBB77&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>恭喜你，你賺到你在這裡的第一筆&lt;color=#FFBB77&gt;報酬&lt;/color&gt;了，接著準備下一單吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">貨幣已經被克拉拉姐姐收走了，&lt;color=#FFBB77&gt;貨幣會被換算成績分，你可以透過計分器看到累積了多少報酬，顧客付款時剩餘的耐心值越高，收到的貨幣也越多&lt;/color&gt;。
+    <t xml:space="preserve">就是這樣，這下核心的修復已經完成，把它&lt;color=#A23400&gt;還給顧客&lt;/color&gt;吧，記得客氣一點，他算是有耐心的一位了
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">這次需要更換的是&lt;color=#FFBB77&gt;原液&lt;/color&gt;，&lt;color=#FFBB77&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
+    <t>每個人的&lt;color=#A23400&gt;耐心是有限的&lt;/color&gt;，你必須在顧客能等待的時間內交予修好的核心，否則&lt;color=#A23400&gt;時間一到他就會直接離開&lt;/color&gt;，咱們也拿不到報酬了，</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你能透過顧客身邊的&lt;color=#A23400&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你，你賺到你在這裡的第一筆&lt;color=#A23400&gt;報酬&lt;/color&gt;了，接著準備下一單吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">貨幣已經被克拉拉姐姐收走了，&lt;color=#A23400&gt;貨幣會被換算成績分，你可以透過計分器看到累積了多少報酬，顧客付款時剩餘的耐心值越高，收到的貨幣也越多&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">你看到四種不同的原料了嗎？&lt;color=#FFBB77&gt;根據顏色放入注射器，它會為你產出相應的原液&lt;/color&gt;。
+    <t xml:space="preserve">你看到四種不同的原料了嗎？&lt;color=#A23400&gt;根據顏色放入注射器，它會為你產出相應的原液&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>沒錯，&lt;color=#FFBB77&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#FFBB77&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>抱歉打擾你們......但是有隻&lt;color=#FFBB77&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#FFBB77&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸好牠的個子小，膽子也不大，&lt;color=#FFBB77&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">要聊等關門後再說，&lt;color=#FFBB77&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=#FFBB77&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
+    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#FFBB77&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
+    <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1152,7 +1152,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1169,7 +1169,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1219,7 +1219,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1236,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1285,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1302,7 +1302,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1351,7 +1351,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1368,7 +1368,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1385,7 +1385,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1434,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1500,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1517,7 +1517,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1534,7 +1534,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1583,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1592,7 +1592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1617,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,14 @@
     <sheet name="第七個說明對話" sheetId="7" r:id="rId7"/>
     <sheet name="第八個說明對話" sheetId="9" r:id="rId8"/>
     <sheet name="第九個說明對話" sheetId="10" r:id="rId9"/>
+    <sheet name="第十個說明對話" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="32">
   <si>
     <t>對話內容</t>
   </si>
@@ -89,18 +90,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>抱歉打擾你們......但是有隻&lt;color=color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=color=#A23400&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸好牠的個子小，膽子也不大，&lt;color=color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -152,10 +141,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -163,6 +148,22 @@
   <si>
     <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉打擾你們......但是有隻&lt;color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#A23400&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1185,6 +1186,58 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="32.25" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
@@ -1219,7 +1272,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1236,7 +1289,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1285,7 +1338,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1302,7 +1355,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1351,7 +1404,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1368,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1385,7 +1438,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1434,7 +1487,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1451,7 +1504,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1500,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1517,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1534,7 +1587,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1583,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1592,7 +1645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1600,7 +1653,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1617,7 +1670,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1683,7 +1736,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1700,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
@@ -1732,29 +1785,12 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="66" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CAE575-C3DE-4F40-815B-F4CC3F9D4076}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="34">
   <si>
     <t>對話內容</t>
   </si>
@@ -164,13 +165,21 @@
   </si>
   <si>
     <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>slide.mp3</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1118,17 +1127,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1145,7 +1154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="81" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1156,13 +1165,13 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1187,18 +1196,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="32.25" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1215,7 +1224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1239,15 +1248,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="39.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="39.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1264,7 +1273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="99" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1281,7 +1290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1306,14 +1315,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1330,7 +1339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="132" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="178.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1371,15 +1380,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="45.875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1396,7 +1405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1413,7 +1422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1430,7 +1439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1454,15 +1463,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="36.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1479,7 +1488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1496,7 +1505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1520,15 +1529,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="47.5" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="47.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1545,7 +1554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1562,7 +1571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1579,7 +1588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1603,15 +1612,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1628,7 +1637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1645,7 +1654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="82.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1662,7 +1671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="81" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1686,15 +1695,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1711,7 +1720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1728,7 +1737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="113.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1752,15 +1761,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="40.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1777,7 +1786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CAE575-C3DE-4F40-815B-F4CC3F9D4076}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="41">
   <si>
     <t>對話內容</t>
   </si>
@@ -46,10 +45,6 @@
   </si>
   <si>
     <t>音檔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>無.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -168,18 +163,50 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Customer.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>slide.mp3</t>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1127,7 +1154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1159,16 +1186,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
@@ -1176,16 +1203,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1223,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1229,16 +1256,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1278,16 +1305,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
@@ -1295,16 +1322,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1342,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1344,16 +1371,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="178.2" x14ac:dyDescent="0.3">
@@ -1361,16 +1388,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1410,16 +1437,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
@@ -1427,16 +1454,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
@@ -1444,16 +1471,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1493,16 +1520,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
@@ -1510,16 +1537,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1529,7 +1556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1559,16 +1586,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
@@ -1576,16 +1603,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
@@ -1593,16 +1620,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1612,7 +1639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1642,16 +1669,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
@@ -1659,16 +1686,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="81" x14ac:dyDescent="0.3">
@@ -1676,16 +1703,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1695,7 +1722,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1725,16 +1752,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="113.4" x14ac:dyDescent="0.3">
@@ -1742,16 +1769,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1761,7 +1788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1791,16 +1818,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -76,130 +76,130 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">把它拿進來，先用&lt;color=#A23400&gt;開殼機&lt;/color&gt;打開，從內部構造才能看出是犯了什麼毛病
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你把損壞核心交給&lt;color=#A23400&gt;開殼機&lt;/color&gt;，它會自動幫你完成作業，&lt;color=#A23400&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;，建議你再忙都要注意耐久值的狀況。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">現在把核心拿到&lt;color=#A23400&gt;工作台&lt;/color&gt;上，這樣能看得更清楚
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">這樣清楚多了，你得透過&lt;color=#A23400&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;，可處理的&lt;color=#A23400&gt;零件有三樣，處理器、電路板和原液&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你成功修好過通訊器，修復這個對你應該沒什麼難的，看到&lt;color=#A23400&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯毛病出在它身上，&lt;color=#A23400&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">就是這樣，這下核心的修復已經完成，把它&lt;color=#A23400&gt;還給顧客&lt;/color&gt;吧，記得客氣一點，他算是有耐心的一位了
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>每個人的&lt;color=#A23400&gt;耐心是有限的&lt;/color&gt;，你必須在顧客能等待的時間內交予修好的核心，否則&lt;color=#A23400&gt;時間一到他就會直接離開&lt;/color&gt;，咱們也拿不到報酬了，</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你能透過顧客身邊的&lt;color=#A23400&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你，你賺到你在這裡的第一筆&lt;color=#A23400&gt;報酬&lt;/color&gt;了，接著準備下一單吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">貨幣已經被克拉拉姐姐收走了，&lt;color=#A23400&gt;貨幣會被換算成績分，你可以透過計分器看到累積了多少報酬，顧客付款時剩餘的耐心值越高，收到的貨幣也越多&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你看到四種不同的原料了嗎？&lt;color=#A23400&gt;根據顏色放入注射器，它會為你產出相應的原液&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
+</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉打擾你們......但是有隻&lt;color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#A23400&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#A23400&gt;損壞核心&lt;/color&gt;，修好它是這間工作室存在的意義
 </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">把它拿進來，先用&lt;color=#A23400&gt;開殼機&lt;/color&gt;打開，從內部構造才能看出是犯了什麼毛病
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你把損壞核心交給&lt;color=#A23400&gt;開殼機&lt;/color&gt;，它會自動幫你完成作業，&lt;color=#A23400&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;，建議你再忙都要注意耐久值的狀況。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">現在把核心拿到&lt;color=#A23400&gt;工作台&lt;/color&gt;上，這樣能看得更清楚
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">這樣清楚多了，你得透過&lt;color=#A23400&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;，可處理的&lt;color=#A23400&gt;零件有三樣，處理器、電路板和原液&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你成功修好過通訊器，修復這個對你應該沒什麼難的，看到&lt;color=#A23400&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯毛病出在它身上，&lt;color=#A23400&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">就是這樣，這下核心的修復已經完成，把它&lt;color=#A23400&gt;還給顧客&lt;/color&gt;吧，記得客氣一點，他算是有耐心的一位了
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每個人的&lt;color=#A23400&gt;耐心是有限的&lt;/color&gt;，你必須在顧客能等待的時間內交予修好的核心，否則&lt;color=#A23400&gt;時間一到他就會直接離開&lt;/color&gt;，咱們也拿不到報酬了，</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你能透過顧客身邊的&lt;color=#A23400&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>恭喜你，你賺到你在這裡的第一筆&lt;color=#A23400&gt;報酬&lt;/color&gt;了，接著準備下一單吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">貨幣已經被克拉拉姐姐收走了，&lt;color=#A23400&gt;貨幣會被換算成績分，你可以透過計分器看到累積了多少報酬，顧客付款時剩餘的耐心值越高，收到的貨幣也越多&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你看到四種不同的原料了嗎？&lt;color=#A23400&gt;根據顏色放入注射器，它會為你產出相應的原液&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>抱歉打擾你們......但是有隻&lt;color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#A23400&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
@@ -1206,10 +1206,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1262,7 +1262,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1308,10 +1308,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1325,10 +1325,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1374,10 +1374,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1391,10 +1391,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1440,10 +1440,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1457,10 +1457,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1474,10 +1474,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1523,10 +1523,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1540,10 +1540,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1589,10 +1589,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1606,10 +1606,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1623,10 +1623,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1672,10 +1672,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1689,10 +1689,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1706,10 +1706,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1758,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1772,10 +1772,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1821,10 +1821,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,34 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DA3EDE-8A6B-43E1-AF29-2288B3826361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="3510" yWindow="3960" windowWidth="21600" windowHeight="11505" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
     <sheet name="第二個說明對話" sheetId="2" r:id="rId2"/>
-    <sheet name="第三個說明對話" sheetId="3" r:id="rId3"/>
-    <sheet name="第四個說明對話" sheetId="4" r:id="rId4"/>
-    <sheet name="第五個說明對話" sheetId="5" r:id="rId5"/>
-    <sheet name="第六個說明對話" sheetId="6" r:id="rId6"/>
-    <sheet name="第七個說明對話" sheetId="7" r:id="rId7"/>
-    <sheet name="第八個說明對話" sheetId="9" r:id="rId8"/>
-    <sheet name="第九個說明對話" sheetId="10" r:id="rId9"/>
-    <sheet name="第十個說明對話" sheetId="11" r:id="rId10"/>
+    <sheet name="第二個說明對話_2" sheetId="13" r:id="rId3"/>
+    <sheet name="第三個說明對話" sheetId="3" r:id="rId4"/>
+    <sheet name="第三個說明對話_2" sheetId="17" r:id="rId5"/>
+    <sheet name="第三個說明對話_3" sheetId="14" r:id="rId6"/>
+    <sheet name="第四個說明對話" sheetId="4" r:id="rId7"/>
+    <sheet name="第四個說明對話_2" sheetId="15" r:id="rId8"/>
+    <sheet name="第五個說明對話" sheetId="5" r:id="rId9"/>
+    <sheet name="第六個說明對話" sheetId="6" r:id="rId10"/>
+    <sheet name="第七個說明對話" sheetId="7" r:id="rId11"/>
+    <sheet name="第八個說明對話" sheetId="9" r:id="rId12"/>
+    <sheet name="第八個說明對話_2" sheetId="16" r:id="rId13"/>
+    <sheet name="第九個說明對話" sheetId="10" r:id="rId14"/>
+    <sheet name="第十個說明對話" sheetId="11" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="51">
   <si>
     <t>對話內容</t>
   </si>
@@ -68,145 +74,175 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>聽起來那些"老主顧"又回來了，你覺得牠們很討厭？等你見到其他"老主顧"就會覺得牠們可愛了。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這就完了？通訊器恢復正常只有一天，昨天成功連絡上我們的也只有那兩位，今天陸陸續續有其他人也成功恢復通訊了，明天有得忙的。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">把它拿進來，先用&lt;color=#A23400&gt;開殼機&lt;/color&gt;打開，從內部構造才能看出是犯了什麼毛病
+    <t>你能透過顧客身邊的&lt;color=#A23400&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉打擾你們......但是有隻&lt;color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>聽起來那些"老主顧"又回來了，你覺得牠們很討厭？等你之後見到其他"老主顧"就會覺得牠們還算是可愛了。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開。現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>看到四種不同的原料了嗎？&lt;color=#A23400&gt;根據顏色放入注射器，它會產出相應的原液&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>算了，要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液，至核心內部進行更換&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這樣清楚多了，你得透過&lt;color=#A23400&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#A23400&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。
 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;應該已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液至核心內部進行更換&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你把損壞核心交給&lt;color=#A23400&gt;開殼機&lt;/color&gt;，它會自動幫你完成作業，&lt;color=#A23400&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;，建議你再忙都要注意耐久值的狀況。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">現在把核心拿到&lt;color=#A23400&gt;工作台&lt;/color&gt;上，這樣能看得更清楚
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">這樣清楚多了，你得透過&lt;color=#A23400&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;，可處理的&lt;color=#A23400&gt;零件有三樣，處理器、電路板和原液&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你成功修好過通訊器，修復這個對你應該沒什麼難的，看到&lt;color=#A23400&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯毛病出在它身上，&lt;color=#A23400&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">就是這樣，這下核心的修復已經完成，把它&lt;color=#A23400&gt;還給顧客&lt;/color&gt;吧，記得客氣一點，他算是有耐心的一位了
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>每個人的&lt;color=#A23400&gt;耐心是有限的&lt;/color&gt;，你必須在顧客能等待的時間內交予修好的核心，否則&lt;color=#A23400&gt;時間一到他就會直接離開&lt;/color&gt;，咱們也拿不到報酬了，</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你能透過顧客身邊的&lt;color=#A23400&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>恭喜你，你賺到你在這裡的第一筆&lt;color=#A23400&gt;報酬&lt;/color&gt;了，接著準備下一單吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">貨幣已經被克拉拉姐姐收走了，&lt;color=#A23400&gt;貨幣會被換算成績分，你可以透過計分器看到累積了多少報酬，顧客付款時剩餘的耐心值越高，收到的貨幣也越多&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你看到四種不同的原料了嗎？&lt;color=#A23400&gt;根據顏色放入注射器，它會為你產出相應的原液&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">完美，這個核心也回復正常了，你也知道該怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，需要更換的是藍色原液，根據我說的自己做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>抱歉打擾你們......但是有隻&lt;color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這種生物博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#A23400&gt;牠的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開，現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#A23400&gt;損壞核心&lt;/color&gt;，修好它是這間工作室存在的意義
-</t>
+    <t>先把它拿進來，用&lt;color=#A23400&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到是出了什麼問題。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在把核芯拿到&lt;color=#A23400&gt;工作台&lt;/color&gt;上，這樣能看得更清楚。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可處理的&lt;color=#A23400&gt;零件將會有三樣，處理器、原液，以及電路板&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這種生物，博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#A23400&gt;牠現在的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>通訊器恢復正常只有一天，昨天成功連絡上我們的也只有那兩位，</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你覺得這就完了？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天陸陸續續有其他人也成功恢復通訊，明天還得有得忙呢。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>完美! 這個核芯也回復正常，你應該知道怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>把損壞核芯交給&lt;color=#A23400&gt;開殼機&lt;/color&gt;後，它會自動幫你完成作業。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#A23400&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議你再忙都要注意耐久值的狀況……</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你成功修好過通訊器，修復這個對你應該不難。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#A23400&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>看到&lt;color=#A23400&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯問題出在它身上......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你必須在顧客能等待的時間內交予修好的核芯，否則&lt;color=#A23400&gt;時間一到他就會直接離開&lt;/color&gt;，我們也拿不到報酬。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#A23400&gt;顧客付款時，剩餘的耐心值越高，同時收到的貨幣也越多&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#A23400&gt;貨幣將會被換算分數，可以透過在旁的計分器看到累積了多少&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你，成功賺到在這裡的第一筆&lt;color=#A23400&gt;報酬&lt;/color&gt;......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉小姐將會幫你代為收走貨幣，緊接著準備下一單吧，營業結束前可別鬆懈。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，因此需要更換的是藍色原液。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>根據剛才說的動手做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>就是這樣，這下核芯修復已經完成，將它&lt;color=#A23400&gt;還給顧客&lt;/color&gt;，記得客氣一點，他還算是有耐心的一位了......</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -793,12 +829,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1154,17 +1196,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="81" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1189,16 +1231,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1206,10 +1248,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1223,18 +1265,330 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="47.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="60.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="57.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3B6682-D821-432B-A44B-0863B0A64DBE}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="60.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="168" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="42.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="60.75" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1251,7 +1605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1259,12 +1613,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1275,15 +1663,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="39.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="122.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1300,7 +1688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1308,29 +1696,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
+      <c r="C3" t="s">
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1342,61 +1747,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195EFFFF-BC81-49FD-8EDF-07350ECFFAE3}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="178.2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="1" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1407,15 +1781,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="45.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="69.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1432,7 +1806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1440,49 +1814,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1490,62 +1831,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810DBC7B-7E02-4D1F-ACC4-827BD741873C}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="3" max="3" width="72.375" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1556,79 +1865,63 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8676AC-56A7-4D9A-B760-EE4A6D10AB64}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="47.44140625" customWidth="1"/>
+    <col min="3" max="3" width="72.75" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
+      <c r="C3" t="s">
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1639,15 +1932,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="45.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1664,54 +1957,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="97.2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="81" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1722,62 +1981,47 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6872ADC-83C0-4270-8C1B-ACE824D006D1}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="53.125" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="113.4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1788,15 +2032,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="119.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1813,7 +2057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1821,12 +2065,63 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DA3EDE-8A6B-43E1-AF29-2288B3826361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3960" windowWidth="21600" windowHeight="11505" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3516" yWindow="3960" windowWidth="21600" windowHeight="11508" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
     <sheet name="第二個說明對話" sheetId="2" r:id="rId2"/>
     <sheet name="第二個說明對話_2" sheetId="13" r:id="rId3"/>
-    <sheet name="第三個說明對話" sheetId="3" r:id="rId4"/>
+    <sheet name="第三個說明對話" sheetId="19" r:id="rId4"/>
     <sheet name="第三個說明對話_2" sheetId="17" r:id="rId5"/>
     <sheet name="第三個說明對話_3" sheetId="14" r:id="rId6"/>
     <sheet name="第四個說明對話" sheetId="4" r:id="rId7"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="51">
   <si>
     <t>對話內容</t>
   </si>
@@ -242,7 +241,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1196,17 +1195,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1223,7 +1222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1240,7 +1239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1265,15 +1264,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="47.5" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="47.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1290,7 +1289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1307,7 +1306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1324,7 +1323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1341,7 +1340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1365,15 +1364,15 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="60.75" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="60.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1390,7 +1389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1407,7 +1406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1424,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1448,15 +1447,15 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="57.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1473,7 +1472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1497,27 +1496,44 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3B6682-D821-432B-A44B-0863B0A64DBE}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="60.5" customWidth="1"/>
+    <col min="3" max="3" width="60.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="168" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
+    <row r="1" spans="1:5" ht="168" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1528,15 +1544,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="42.25" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1553,7 +1569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1577,18 +1593,18 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="60.75" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="60.77734375" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1605,7 +1621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1622,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1639,7 +1655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1663,15 +1679,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="122.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1688,7 +1704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1705,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1722,7 +1738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1747,30 +1763,47 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195EFFFF-BC81-49FD-8EDF-07350ECFFAE3}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1781,15 +1814,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="69.125" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1806,7 +1839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1817,13 +1850,12 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1831,30 +1863,47 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810DBC7B-7E02-4D1F-ACC4-827BD741873C}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="72.375" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="3" max="3" width="72.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1865,63 +1914,80 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8676AC-56A7-4D9A-B760-EE4A6D10AB64}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="72.75" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="3" max="3" width="72.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
+    <row r="1" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1932,15 +1998,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="45.875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1957,7 +2023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1981,47 +2047,64 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6872ADC-83C0-4270-8C1B-ACE824D006D1}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="53.125" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
-    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="53.109375" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
+    <row r="1" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2032,15 +2115,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="119.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="119.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2057,7 +2140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2074,7 +2157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2091,7 +2174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2108,7 +2191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EFA564-C146-4C6F-AB68-3A3342487AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3516" yWindow="3960" windowWidth="21600" windowHeight="11508" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="52">
   <si>
     <t>對話內容</t>
   </si>
@@ -73,14 +74,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>你能透過顧客身邊的&lt;color=#A23400&gt;耐心條&lt;/color&gt;判斷他將會停留多久。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>抱歉打擾你們......但是有隻&lt;color=#A23400&gt;”小個子”在破壞注射器&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>.mp3</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -121,128 +114,162 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>聽起來那些"老主顧"又回來了，你覺得牠們很討厭？等你之後見到其他"老主顧"就會覺得牠們還算是可愛了。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸好牠的個子小，膽子也不大，&lt;color=#A23400&gt;只要您動手驅逐牠就會離開。現在請點擊"小個子"，趕走這個搗蛋鬼！&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這次需要更換的是&lt;color=#A23400&gt;原液&lt;/color&gt;，&lt;color=#A23400&gt;原液需要使用注射器練成，總共有四個種類，呈現出四種不同的顏色&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>看到四種不同的原料了嗎？&lt;color=#A23400&gt;根據顏色放入注射器，它會產出相應的原液&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>算了，要聊等關門後再說，&lt;color=color=#A23400&gt;注射器&lt;/color&gt;已經完成作業了，&lt;color=color=#A23400&gt;跟更換其他零件的步驟一樣，拖曳提煉好的藍色原液，至核心內部進行更換&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這樣清楚多了，你得透過&lt;color=#A23400&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#A23400&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>先把它拿進來，用&lt;color=#A23400&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到是出了什麼問題。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在把核芯拿到&lt;color=#A23400&gt;工作台&lt;/color&gt;上，這樣能看得更清楚。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>可處理的&lt;color=#A23400&gt;零件將會有三樣，處理器、原液，以及電路板&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這種生物，博士您應該見過，他們會到處收集各種資源送入牠們的巢穴，&lt;color=#A23400&gt;牠現在的目的是機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>通訊器恢復正常只有一天，昨天成功連絡上我們的也只有那兩位，</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你覺得這就完了？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>今天陸陸續續有其他人也成功恢復通訊，明天還得有得忙呢。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>完美! 這個核芯也回復正常，你應該知道怎麼做，&lt;color=#A23400&gt;將它還給顧客，準備關門吧&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>把損壞核芯交給&lt;color=#A23400&gt;開殼機&lt;/color&gt;後，它會自動幫你完成作業。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#A23400&gt;任何機械在運作時皆會消耗耐久值，耐久值到底會導致機械癱瘓，失去作用&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>建議你再忙都要注意耐久值的狀況……</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>你成功修好過通訊器，修復這個對你應該不難。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;color=#A23400&gt;換個新的，記得選形狀一樣的，拖曳過去進行更換&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>看到&lt;color=#A23400&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯問題出在它身上......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>你必須在顧客能等待的時間內交予修好的核芯，否則&lt;color=#A23400&gt;時間一到他就會直接離開&lt;/color&gt;，我們也拿不到報酬。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#A23400&gt;顧客付款時，剩餘的耐心值越高，同時收到的貨幣也越多&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#A23400&gt;貨幣將會被換算分數，可以透過在旁的計分器看到累積了多少&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>恭喜你，成功賺到在這裡的第一筆&lt;color=#A23400&gt;報酬&lt;/color&gt;......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>克拉拉小姐將會幫你代為收走貨幣，緊接著準備下一單吧，營業結束前可別鬆懈。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>沒錯，&lt;color=#A23400&gt;損壞的原液試管內還殘留了一點藍色&lt;/color&gt;，因此需要更換的是藍色原液。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>根據剛才說的動手做看看，&lt;color=#A23400&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>就是這樣，這下核芯修復已經完成，將它&lt;color=#A23400&gt;還給顧客&lt;/color&gt;，記得客氣一點，他還算是有耐心的一位了......</t>
+    <t>把損壞核芯交給&lt;color=#AC0000&gt;開殼機&lt;/color&gt;後，它會自動幫你完成作業。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作台&lt;/color&gt;上，這樣能看得更清楚。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這樣清楚多了，你得透過&lt;color=#AC0000&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可處理的零件將會有三樣，&lt;color=#AC0000&gt;處理器、原液，以及電路板&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>看到&lt;color=#AC0000&gt;處理器&lt;/color&gt;的樣子了嗎？很明顯問題出在它身上......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>就是這樣，這下核芯修復已經完成，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，記得客氣一點，他還算是有耐心的一位了......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你必須在顧客能等待的時間內交予修好的核芯，否則&lt;color=#AC0000&gt;時間一到他就會直接離開&lt;/color&gt;，我們也拿不到報酬。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天陸續還有其他人成功恢復通訊，明天還得有得忙......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>你覺得這就結束了？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>聽起來那些"老朋友"又回來了?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>等見到其他"熟客"後，你就會覺得牠們還算是可愛......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#AC0000&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>先把它拿進來，用&lt;color=#AC0000&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到出了什麼問題。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>任何機械在運作時皆會&lt;color=#AC0000&gt;消耗耐久值，當耐久值到底會導致機械癱瘓，進而失去作用&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議你再忙的狀況下都要注意&lt;color=#AC0000&gt;機械的耐久值&lt;/color&gt;......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你能透過顧客身邊的&lt;color=#AC0000&gt;耐心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;判斷他將會停留多久。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#AC0000&gt;貨幣將會被換算分數&lt;/color&gt;，可以透過在旁的&lt;color=#AC0000&gt;計分器&lt;/color&gt;看到累積了多少。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>顧客付款時，剩餘的&lt;color=#AC0000&gt;耐心值越高，同時收到的貨幣也越多&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這次需要更換的是&lt;color=#AC0000&gt;原液&lt;/color&gt;，原液&lt;color=#AC0000&gt;需要使用注射器練成，共有四種，各呈現出不同顏色&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>看到四種不同顏色的原料了嗎？&lt;color=#AC0000&gt;放入注射器後，將會產出與原料相應顏色的原液&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>正如所見，現在損壞的原液試管內還殘留了一點&lt;color=#AC0000&gt;藍色&lt;/color&gt;，因此需要更換的是&lt;color=#AC0000&gt;藍色原液&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>根據剛才所說的動手做看看，&lt;color=#AC0000&gt;拖曳原料放入注射器&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這種生物，博士您應該見過，牠們會到處收集各種資源送入牠們的巢穴，&lt;color=#AC0000&gt;牠現在的目的是偷走機器裡的零件，如果讓牠得手的話，機器的耐久值會大幅下降&lt;/color&gt;！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉打擾你們......但是有隻&lt;color=#AC0000&gt;"小個子"&lt;/color&gt;在破壞注射器！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸好牠的個子小，膽子也不大，只要您動手驅逐牠就會離開。&lt;color=#AC0000&gt;現在請連續點擊"小個子"&lt;/color&gt;，趕走這個搗蛋鬼！</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>完美! 這個核芯也回復正常，你應該知道怎麼做，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，準備關門吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>換個新的，記得選&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;，&lt;color=#AC0000&gt;拖曳過去進行更換&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前通訊器恢復正常只有一天，昨天成功連絡上我們的也只有那兩位......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你，成功賺到在這裡的&lt;color=#AC0000&gt;第一筆報酬&lt;/color&gt;......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>算了，要聊等關門後再說，&lt;color=#AC0000&gt;注射器&lt;/color&gt;已經完成作業了，跟更換其他零件的步驟一樣，&lt;color=#AC0000&gt;拖曳提煉好的藍色原液，至核心內部進行更換&lt;/color&gt;。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -402,6 +429,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -888,6 +922,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFAC0000"/>
+      <color rgb="FFA91313"/>
+      <color rgb="FFB82C00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1195,17 +1236,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1222,7 +1263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1230,27 +1271,27 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1264,15 +1305,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="47.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="47.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1289,7 +1330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1297,16 +1338,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1314,16 +1355,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1331,16 +1372,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1348,10 +1389,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -1364,15 +1405,15 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="60.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="60.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1389,7 +1430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1397,16 +1438,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1414,16 +1455,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1431,10 +1472,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1447,15 +1488,15 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="57.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="57.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1472,7 +1513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1480,12 +1521,29 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1496,14 +1554,14 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="60.44140625" customWidth="1"/>
+    <col min="3" max="3" width="60.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="168" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1520,7 +1578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1528,10 +1586,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1544,15 +1602,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="42.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="42.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1569,7 +1627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1577,10 +1635,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1593,18 +1651,18 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
-    <col min="3" max="3" width="60.77734375" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1621,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1629,16 +1687,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1646,16 +1704,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1663,10 +1721,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1679,15 +1737,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="122.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="122.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1704,7 +1762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1712,16 +1770,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1729,16 +1787,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1746,10 +1804,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1763,17 +1821,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="35.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1790,7 +1848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1798,10 +1856,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -1814,15 +1872,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1839,7 +1897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1847,10 +1905,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1863,17 +1921,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" customWidth="1"/>
-    <col min="3" max="3" width="72.33203125" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="3" max="3" width="72.375" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1890,7 +1948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1898,10 +1956,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1914,16 +1972,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="72.77734375" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1940,7 +1998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1948,16 +2006,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1965,16 +2023,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1982,10 +2040,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -1998,15 +2056,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="45.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="45.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2023,7 +2081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2031,10 +2089,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -2047,17 +2105,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="53.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.77734375" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="53.125" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2074,7 +2132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2082,16 +2140,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2099,10 +2157,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -2115,15 +2173,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="119.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="119.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2140,7 +2198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2148,16 +2206,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2165,16 +2223,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2182,16 +2240,16 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2199,10 +2257,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EFA564-C146-4C6F-AB68-3A3342487AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2B462A-BE31-4F13-A282-E4EB78976285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="53">
   <si>
     <t>對話內容</t>
   </si>
@@ -163,10 +163,6 @@
   </si>
   <si>
     <t>等見到其他"熟客"後，你就會覺得牠們還算是可愛......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#AC0000&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -245,10 +241,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>完美! 這個核芯也回復正常，你應該知道怎麼做，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，準備關門吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>換個新的，記得選&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;，&lt;color=#AC0000&gt;拖曳過去進行更換&lt;/color&gt;。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -262,6 +254,18 @@
   </si>
   <si>
     <t>算了，要聊等關門後再說，&lt;color=#AC0000&gt;注射器&lt;/color&gt;已經完成作業了，跟更換其他零件的步驟一樣，&lt;color=#AC0000&gt;拖曳提煉好的藍色原液，至核心內部進行更換&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#AC0000&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完美! </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這個核芯也回復正常，你應該知道怎麼做，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，準備關門吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1271,7 +1275,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1288,7 +1292,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1338,7 +1342,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1355,7 +1359,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1372,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1389,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1438,7 +1442,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1455,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1472,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1586,7 +1590,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1603,11 +1607,11 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="42.25" customWidth="1"/>
+    <col min="3" max="3" width="92.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1635,12 +1639,29 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1704,7 +1725,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1787,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1804,7 +1825,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -2040,7 +2061,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -2115,7 +2136,7 @@
     <col min="5" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2140,7 +2161,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -2206,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -2223,7 +2244,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -2240,7 +2261,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -8,33 +8,42 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2B462A-BE31-4F13-A282-E4EB78976285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71A8BF1-CDB1-45C1-9DB2-57E69F434097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-180" yWindow="0" windowWidth="18255" windowHeight="16305" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
     <sheet name="第二個說明對話" sheetId="2" r:id="rId2"/>
     <sheet name="第二個說明對話_2" sheetId="13" r:id="rId3"/>
-    <sheet name="第三個說明對話" sheetId="19" r:id="rId4"/>
-    <sheet name="第三個說明對話_2" sheetId="17" r:id="rId5"/>
-    <sheet name="第三個說明對話_3" sheetId="14" r:id="rId6"/>
-    <sheet name="第四個說明對話" sheetId="4" r:id="rId7"/>
-    <sheet name="第四個說明對話_2" sheetId="15" r:id="rId8"/>
-    <sheet name="第五個說明對話" sheetId="5" r:id="rId9"/>
-    <sheet name="第六個說明對話" sheetId="6" r:id="rId10"/>
-    <sheet name="第七個說明對話" sheetId="7" r:id="rId11"/>
-    <sheet name="第八個說明對話" sheetId="9" r:id="rId12"/>
-    <sheet name="第八個說明對話_2" sheetId="16" r:id="rId13"/>
-    <sheet name="第九個說明對話" sheetId="10" r:id="rId14"/>
-    <sheet name="第十個說明對話" sheetId="11" r:id="rId15"/>
+    <sheet name="第二個說明對話_3" sheetId="23" r:id="rId4"/>
+    <sheet name="第二個說明對話_4" sheetId="20" r:id="rId5"/>
+    <sheet name="第三個說明對話" sheetId="19" r:id="rId6"/>
+    <sheet name="第三個說明對話_2" sheetId="17" r:id="rId7"/>
+    <sheet name="第三個說明對話_3" sheetId="14" r:id="rId8"/>
+    <sheet name="第三個說明對話_4" sheetId="21" r:id="rId9"/>
+    <sheet name="第三個說明對話_5" sheetId="24" r:id="rId10"/>
+    <sheet name="第三個說明對話_6" sheetId="25" r:id="rId11"/>
+    <sheet name="第三個說明對話_7" sheetId="26" r:id="rId12"/>
+    <sheet name="第三個說明對話_8" sheetId="27" r:id="rId13"/>
+    <sheet name="第四個說明對話" sheetId="4" r:id="rId14"/>
+    <sheet name="第四個說明對話_2" sheetId="15" r:id="rId15"/>
+    <sheet name="第五個說明對話" sheetId="5" r:id="rId16"/>
+    <sheet name="第六個說明對話" sheetId="6" r:id="rId17"/>
+    <sheet name="第七個說明對話" sheetId="7" r:id="rId18"/>
+    <sheet name="第八個說明對話" sheetId="9" r:id="rId19"/>
+    <sheet name="第八個說明對話_2" sheetId="16" r:id="rId20"/>
+    <sheet name="第八個說明對話_3" sheetId="28" r:id="rId21"/>
+    <sheet name="第八個說明對話_4" sheetId="29" r:id="rId22"/>
+    <sheet name="第九個說明對話" sheetId="10" r:id="rId23"/>
+    <sheet name="第十個說明對話" sheetId="11" r:id="rId24"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="75">
   <si>
     <t>對話內容</t>
   </si>
@@ -123,10 +132,6 @@
   </si>
   <si>
     <t>把損壞核芯交給&lt;color=#AC0000&gt;開殼機&lt;/color&gt;後，它會自動幫你完成作業。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作台&lt;/color&gt;上，這樣能看得更清楚。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -241,10 +246,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>換個新的，記得選&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;，&lt;color=#AC0000&gt;拖曳過去進行更換&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>目前通訊器恢復正常只有一天，昨天成功連絡上我們的也只有那兩位......</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -266,6 +267,102 @@
   </si>
   <si>
     <t>這個核芯也回復正常，你應該知道怎麼做，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，準備關門吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對話內容</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作檯&lt;/color&gt;上，這樣能看得更清楚。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在把注意力放回工作臺上的核芯，繼續剛才的修理流程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在得做個新的&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;的處理器，&lt;color=#AC0000&gt;拖曳過去進行更換&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>我們需要使用&lt;color=#AC0000&gt;處理器製作機&lt;/color&gt;──就是那隻看似&lt;color=#AC0000&gt;兔子&lt;/color&gt;的生物，你也可以這麼稱呼它，更簡短直觀一點。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔子需要一點時間才能將處理器製作完成。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在這期間，另外有件事要讓你知道。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在兔子已經完成了它的任務，讓我們把手頭上的工作結束吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹也已經完成它的工作了。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>──喔，你好像很在意&lt;color=#AC0000&gt;耐久值&lt;/color&gt;的問題？當然，&lt;color=#AC0000&gt;他們不會自己回復&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿起&lt;color=#AC0000&gt;修理工具，拖曳至機器上&lt;/color&gt;，即可進行修復，當然不只是開殼機，&lt;color=#AC0000&gt;任何有耐久值的機器都可以用同樣的方法修復&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>機械進入&lt;color=#AC0000&gt;修理狀態，會隨時間逐步恢復耐久值，直到恢復至上限為止。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>機械的&lt;color=#AC0000&gt;修復與工作不能同進行&lt;/color&gt;，你依然可以給修復中的機器分配工作，但&lt;color=#AC0000&gt;修復進度也會立刻停止，直到再次使用修理工具&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊與&lt;color=#AC0000&gt;壞掉處理器相同的形狀&lt;/color&gt;，製作出的成品才能進行替換。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>看見&lt;color=#AC0000&gt;兔耳朵上顯示的形狀&lt;/color&gt;了嗎？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以將事先做好的零件的物品放置在這裡，&lt;color=#AC0000&gt;左邊可放置原液，右邊可放置處理器零件&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外你應該也注意到了，&lt;color=#AC0000&gt;存放的位置是有限&lt;/color&gt;的。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果預先準備的&lt;color=#AC0000&gt;零件或試劑有錯&lt;/color&gt;，可以按下&lt;color=#AC0000&gt;回收按鈕&lt;/color&gt;，替你清出多的存放空間。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>謹記，我們現在的資源&lt;color=#AC0000&gt;只夠回收兩次錯誤物件&lt;/color&gt;，好好運用你的機會吧......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將&lt;color=#AC0000&gt;新的處理器零件拖曳入核芯中替換&lt;/color&gt;，完成修復。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>話說你也注意到了吧，這次的核芯不是只有一處損壞，它的&lt;color=#AC0000&gt;電路板也燒毀了&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將電路板拿出，交給&lt;color=#AC0000&gt;電路修復台&lt;/color&gt;，但看你一副覺得拗口的樣子，可以同樣簡稱牠&lt;color=#AC0000&gt;螃蟹&lt;/color&gt;就好。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹與最開始講解的開殼機一樣，&lt;color=#AC0000&gt;只要你將物件交給它，就會自動完成任務&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將&lt;color=#AC0000&gt;回復正常的電路板移入核芯內&lt;/color&gt;。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -866,7 +963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -877,7 +974,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1275,7 +1375,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1292,7 +1392,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1309,6 +1409,529 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DFDF66-8207-48D3-BD87-2BB439DB4B3C}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.75" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="77" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493C3972-8A58-47A8-A289-E9EEE2A3DAB7}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F991E829-2318-4190-8793-1158940C7560}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="112.875" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E6DFFC-22A9-4183-96F5-08535D4E88B7}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="45.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="53.125" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="119.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -1342,7 +1965,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1359,7 +1982,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1376,7 +1999,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1393,7 +2016,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1408,7 +2031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -1442,7 +2065,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1459,7 +2082,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1476,7 +2099,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1491,7 +2114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -1525,7 +2148,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1542,212 +2165,12 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="60.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="92.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="66" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1808,7 +2231,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1825,7 +2248,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1841,18 +2264,393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="82" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0BC395-D5A6-4158-8292-3BA8CEBB7737}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="120.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="17" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="18" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{522E6FB5-28C2-47D1-9526-FC77C66D43E0}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="111.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="19" hidden="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="92.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
     <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="3" max="3" width="101.375" customWidth="1"/>
     <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1869,7 +2667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1877,12 +2675,29 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1893,15 +2708,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F49BFB05-C648-4F26-98E0-4DED77887FCB}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
-    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="15.375" customWidth="1"/>
+    <col min="3" max="3" width="143.75" customWidth="1"/>
+    <col min="4" max="4" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1909,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -1918,20 +2735,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1942,6 +2759,140 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30231728-4CE0-4F7A-859B-1AC09F729BAB}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="151.125" customWidth="1"/>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="3" max="3" width="89" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -1977,140 +2928,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="92" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="45.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -2126,17 +2944,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="53.125" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
-    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="122.25" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2153,7 +2971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2161,29 +2979,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
+      <c r="C3" t="s">
+        <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2194,15 +3029,18 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537D6E28-CEF2-4B07-B126-273C6695BC07}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="119.375" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="134.25" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2226,64 +3064,13 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>48</v>
+      <c r="C2" t="s">
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71A8BF1-CDB1-45C1-9DB2-57E69F434097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="0" windowWidth="18255" windowHeight="16305" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-180" yWindow="0" windowWidth="18252" windowHeight="16308" firstSheet="20" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
     <sheet name="第二個說明對話" sheetId="2" r:id="rId2"/>
     <sheet name="第二個說明對話_2" sheetId="13" r:id="rId3"/>
-    <sheet name="第二個說明對話_3" sheetId="23" r:id="rId4"/>
+    <sheet name="第二個說明對話_3" sheetId="32" r:id="rId4"/>
     <sheet name="第二個說明對話_4" sheetId="20" r:id="rId5"/>
     <sheet name="第三個說明對話" sheetId="19" r:id="rId6"/>
     <sheet name="第三個說明對話_2" sheetId="17" r:id="rId7"/>
@@ -30,20 +29,21 @@
     <sheet name="第四個說明對話_2" sheetId="15" r:id="rId15"/>
     <sheet name="第五個說明對話" sheetId="5" r:id="rId16"/>
     <sheet name="第六個說明對話" sheetId="6" r:id="rId17"/>
-    <sheet name="第七個說明對話" sheetId="7" r:id="rId18"/>
-    <sheet name="第八個說明對話" sheetId="9" r:id="rId19"/>
-    <sheet name="第八個說明對話_2" sheetId="16" r:id="rId20"/>
-    <sheet name="第八個說明對話_3" sheetId="28" r:id="rId21"/>
-    <sheet name="第八個說明對話_4" sheetId="29" r:id="rId22"/>
-    <sheet name="第九個說明對話" sheetId="10" r:id="rId23"/>
-    <sheet name="第十個說明對話" sheetId="11" r:id="rId24"/>
+    <sheet name="第六個說明對話_2" sheetId="30" r:id="rId18"/>
+    <sheet name="第七個說明對話" sheetId="7" r:id="rId19"/>
+    <sheet name="第八個說明對話" sheetId="9" r:id="rId20"/>
+    <sheet name="第八個說明對話_2" sheetId="16" r:id="rId21"/>
+    <sheet name="第八個說明對話_3" sheetId="33" r:id="rId22"/>
+    <sheet name="第八個說明對話_4" sheetId="34" r:id="rId23"/>
+    <sheet name="第九個說明對話" sheetId="10" r:id="rId24"/>
+    <sheet name="第十個說明對話" sheetId="11" r:id="rId25"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="101">
   <si>
     <t>對話內容</t>
   </si>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Customer.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -119,10 +115,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>你成功修好過通訊器，修復這個對你應該不難。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -168,10 +160,6 @@
   </si>
   <si>
     <t>等見到其他"熟客"後，你就會覺得牠們還算是可愛......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>先把它拿進來，用&lt;color=#AC0000&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到出了什麼問題。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -258,71 +246,123 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">完美! </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>這個核芯也回復正常，你應該知道怎麼做，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，準備關門吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>對話內容</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作檯&lt;/color&gt;上，這樣能看得更清楚。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在把注意力放回工作臺上的核芯，繼續剛才的修理流程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>我們需要使用&lt;color=#AC0000&gt;處理器製作機&lt;/color&gt;──就是那隻看似&lt;color=#AC0000&gt;兔子&lt;/color&gt;的生物，你也可以這麼稱呼它，更簡短直觀一點。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔子需要一點時間才能將處理器製作完成。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在這期間，另外有件事要讓你知道。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在兔子已經完成了它的任務，讓我們把手頭上的工作結束吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹也已經完成它的工作了。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>──喔，你好像很在意&lt;color=#AC0000&gt;耐久值&lt;/color&gt;的問題？當然，&lt;color=#AC0000&gt;他們不會自己回復&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>機械的&lt;color=#AC0000&gt;修復與工作不能同進行&lt;/color&gt;，你依然可以給修復中的機器分配工作，但&lt;color=#AC0000&gt;修復進度也會立刻停止，直到再次使用修理工具&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊與&lt;color=#AC0000&gt;壞掉處理器相同的形狀&lt;/color&gt;，製作出的成品才能進行替換。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以將事先做好的零件的物品放置在這裡，&lt;color=#AC0000&gt;左邊可放置原液，右邊可放置處理器零件&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外你應該也注意到了，&lt;color=#AC0000&gt;存放的位置是有限&lt;/color&gt;的。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果預先準備的&lt;color=#AC0000&gt;零件或試劑有錯&lt;/color&gt;，可以按下&lt;color=#AC0000&gt;回收按鈕&lt;/color&gt;，替你清出多的存放空間。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>謹記，我們現在的資源&lt;color=#AC0000&gt;只夠回收兩次錯誤物件&lt;/color&gt;，好好運用你的機會吧......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將&lt;color=#AC0000&gt;新的處理器零件拖曳入核芯中替換&lt;/color&gt;，完成修復。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>話說你也注意到了吧，這次的核芯不是只有一處損壞，它的&lt;color=#AC0000&gt;電路板也燒毀了&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將電路板拿出，交給&lt;color=#AC0000&gt;電路修復台&lt;/color&gt;，但看你一副覺得拗口的樣子，可以同樣簡稱牠&lt;color=#AC0000&gt;螃蟹&lt;/color&gt;就好。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹與最開始講解的開殼機一樣，&lt;color=#AC0000&gt;只要你將物件交給它，就會自動完成任務&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>音檔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#AC0000&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">完美! </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這個核芯也回復正常，你應該知道怎麼做，將它&lt;color=#AC0000&gt;還給顧客&lt;/color&gt;，準備關門吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>對話內容</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作檯&lt;/color&gt;上，這樣能看得更清楚。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在把注意力放回工作臺上的核芯，繼續剛才的修理流程。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在得做個新的&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;的處理器，&lt;color=#AC0000&gt;拖曳過去進行更換&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我們需要使用&lt;color=#AC0000&gt;處理器製作機&lt;/color&gt;──就是那隻看似&lt;color=#AC0000&gt;兔子&lt;/color&gt;的生物，你也可以這麼稱呼它，更簡短直觀一點。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>兔子需要一點時間才能將處理器製作完成。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在這期間，另外有件事要讓你知道。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在兔子已經完成了它的任務，讓我們把手頭上的工作結束吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>螃蟹也已經完成它的工作了。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>──喔，你好像很在意&lt;color=#AC0000&gt;耐久值&lt;/color&gt;的問題？當然，&lt;color=#AC0000&gt;他們不會自己回復&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>拿起&lt;color=#AC0000&gt;修理工具，拖曳至機器上&lt;/color&gt;，即可進行修復，當然不只是開殼機，&lt;color=#AC0000&gt;任何有耐久值的機器都可以用同樣的方法修復&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>機械進入&lt;color=#AC0000&gt;修理狀態，會隨時間逐步恢復耐久值，直到恢復至上限為止。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>機械的&lt;color=#AC0000&gt;修復與工作不能同進行&lt;/color&gt;，你依然可以給修復中的機器分配工作，但&lt;color=#AC0000&gt;修復進度也會立刻停止，直到再次使用修理工具&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>點擊與&lt;color=#AC0000&gt;壞掉處理器相同的形狀&lt;/color&gt;，製作出的成品才能進行替換。</t>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>先把它拿進來，用&lt;color=#AC0000&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到出了什麼問題。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在得做個新的&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;的處理器。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -330,47 +370,110 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>可以將事先做好的零件的物品放置在這裡，&lt;color=#AC0000&gt;左邊可放置原液，右邊可放置處理器零件&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>另外你應該也注意到了，&lt;color=#AC0000&gt;存放的位置是有限&lt;/color&gt;的。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果預先準備的&lt;color=#AC0000&gt;零件或試劑有錯&lt;/color&gt;，可以按下&lt;color=#AC0000&gt;回收按鈕&lt;/color&gt;，替你清出多的存放空間。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>謹記，我們現在的資源&lt;color=#AC0000&gt;只夠回收兩次錯誤物件&lt;/color&gt;，好好運用你的機會吧......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>將&lt;color=#AC0000&gt;新的處理器零件拖曳入核芯中替換&lt;/color&gt;，完成修復。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>話說你也注意到了吧，這次的核芯不是只有一處損壞，它的&lt;color=#AC0000&gt;電路板也燒毀了&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>將電路板拿出，交給&lt;color=#AC0000&gt;電路修復台&lt;/color&gt;，但看你一副覺得拗口的樣子，可以同樣簡稱牠&lt;color=#AC0000&gt;螃蟹&lt;/color&gt;就好。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>螃蟹與最開始講解的開殼機一樣，&lt;color=#AC0000&gt;只要你將物件交給它，就會自動完成任務&lt;/color&gt;。</t>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一位客人來了，照方才我教你的流程走一遍，確認這個核芯是出了什麼問題。</t>
+  </si>
+  <si>
+    <t>機械進入&lt;color=#AC0000&gt;修理狀態，會隨時間逐步恢復耐久值，直到恢復至上限為止&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿起&lt;color=#AC0000&gt;修理工具&lt;/color&gt;，即可進行修復，當然不只是開殼機，&lt;color=#AC0000&gt;任何有耐久值的機器都可以用同樣的方法修復&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>音檔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>音檔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>將&lt;color=#AC0000&gt;回復正常的電路板移入核芯內&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -536,6 +639,12 @@
       <name val="Microsoft JhengHei UI"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -963,7 +1072,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -978,6 +1087,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1340,19 +1452,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1361,44 +1473,44 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1409,17 +1521,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DFDF66-8207-48D3-BD87-2BB439DB4B3C}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.75" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="4.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
     <col min="3" max="3" width="77" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1436,7 +1548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1444,16 +1556,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1461,46 +1573,12 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1511,17 +1589,17 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493C3972-8A58-47A8-A289-E9EEE2A3DAB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1538,7 +1616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1546,16 +1624,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1563,10 +1641,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1579,17 +1657,17 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F991E829-2318-4190-8793-1158940C7560}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="112.875" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="112.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1614,16 +1692,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1631,10 +1709,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1647,17 +1725,17 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E6DFFC-22A9-4183-96F5-08535D4E88B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1674,7 +1752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1682,16 +1760,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1699,10 +1777,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1715,15 +1793,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="45.875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1740,7 +1818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1748,10 +1826,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1764,17 +1842,17 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="53.125" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
-    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="53.109375" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1791,7 +1869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1799,16 +1877,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1816,10 +1894,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -1832,15 +1910,15 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="119.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="119.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1857,7 +1935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1865,16 +1943,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1882,16 +1960,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1899,16 +1977,16 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1916,10 +1994,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -1932,15 +2010,15 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="47.5" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="47.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1957,7 +2035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1965,16 +2043,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1982,16 +2060,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1999,16 +2077,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2016,10 +2094,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -2032,17 +2110,16 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="60.75" customWidth="1"/>
+    <col min="3" max="3" width="87.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2057,54 +2134,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>81</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2115,15 +2158,15 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="57.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="60.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2140,37 +2183,54 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2181,15 +2241,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="122.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2206,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2214,16 +2274,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2231,16 +2291,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2248,10 +2308,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -2265,16 +2325,15 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="82" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2291,7 +2350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2299,12 +2358,29 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2315,15 +2391,16 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0BC395-D5A6-4158-8292-3BA8CEBB7737}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="120.5" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="82" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2340,7 +2417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2348,61 +2425,15 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="17" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="18" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2410,17 +2441,17 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{522E6FB5-28C2-47D1-9526-FC77C66D43E0}">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="111.875" customWidth="1"/>
+    <col min="3" max="3" width="144.5546875" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2429,58 +2460,63 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="19" hidden="1" x14ac:dyDescent="0.25"/>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2488,17 +2524,17 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="92.875" customWidth="1"/>
+    <col min="3" max="3" width="77.21875" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2507,44 +2543,44 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="81" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2554,18 +2590,84 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="92.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
     <col min="3" max="3" width="66" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2582,7 +2684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2590,16 +2692,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2607,16 +2709,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2624,10 +2726,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -2640,17 +2742,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="101.375" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="101.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2667,7 +2769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2675,16 +2777,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2692,10 +2794,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -2708,17 +2810,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F49BFB05-C648-4F26-98E0-4DED77887FCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.625" customWidth="1"/>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="3" width="143.75" customWidth="1"/>
-    <col min="4" max="4" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="82.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2726,27 +2825,27 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
+      <c r="C2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -2759,16 +2858,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30231728-4CE0-4F7A-859B-1AC09F729BAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="151.125" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="151.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2776,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -2785,7 +2884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2793,16 +2892,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2810,10 +2909,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -2826,16 +2925,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="89" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2852,7 +2951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2860,16 +2959,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2877,10 +2976,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -2893,17 +2992,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="72.375" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="3" max="3" width="72.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2920,7 +3019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2928,10 +3027,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -2944,17 +3043,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.25" customWidth="1"/>
-    <col min="3" max="3" width="122.25" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="122.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2971,7 +3070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2979,16 +3078,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2996,16 +3095,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3013,10 +3112,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3029,18 +3128,18 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537D6E28-CEF2-4B07-B126-273C6695BC07}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="13.25" customWidth="1"/>
-    <col min="3" max="3" width="134.25" customWidth="1"/>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="134.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3057,7 +3156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3065,13 +3164,47 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAF8B00-BE49-442E-952E-D49E3191A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="0" windowWidth="18252" windowHeight="16308" firstSheet="20" activeTab="24"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="15" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -472,7 +473,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1452,17 +1453,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -1479,7 +1480,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1496,7 +1497,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1521,17 +1522,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="4.75" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
     <col min="3" max="3" width="77" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1548,7 +1549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1565,7 +1566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1589,17 +1590,17 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="100.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1633,7 +1634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1657,17 +1658,17 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="112.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="112.875" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1684,7 +1685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1701,7 +1702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1725,17 +1726,17 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="100.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1752,7 +1753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1769,7 +1770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1793,15 +1794,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="45.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="45.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1842,17 +1843,17 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="53.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.77734375" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="53.125" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1869,7 +1870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1886,7 +1887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1910,15 +1911,15 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="119.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="119.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1935,7 +1936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1969,7 +1970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1986,7 +1987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2010,15 +2011,15 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="47.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="47.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2052,7 +2053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2069,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2086,7 +2087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2110,14 +2111,15 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="87.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="87.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -2134,7 +2136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2158,15 +2160,15 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="60.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="60.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2183,7 +2185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2200,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2217,7 +2219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2241,15 +2243,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="122.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="122.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2266,7 +2268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2283,7 +2285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2300,7 +2302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2325,15 +2327,15 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="57.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="57.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2350,7 +2352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2367,7 +2369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2391,16 +2393,16 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
     <col min="3" max="3" width="82" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2417,7 +2419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2441,15 +2443,15 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="144.5546875" customWidth="1"/>
-    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="3" max="3" width="144.5" customWidth="1"/>
+    <col min="4" max="4" width="41.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -2466,7 +2468,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2483,7 +2485,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2500,7 +2502,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2524,15 +2526,15 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="77.21875" customWidth="1"/>
-    <col min="4" max="4" width="40.5546875" customWidth="1"/>
+    <col min="3" max="3" width="77.25" customWidth="1"/>
+    <col min="4" max="4" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>94</v>
       </c>
@@ -2549,7 +2551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="81" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2566,7 +2568,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2590,15 +2592,15 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="92.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="92.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2615,7 +2617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2632,7 +2634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2656,18 +2658,18 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
     <col min="3" max="3" width="66" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2684,7 +2686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2701,7 +2703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2718,7 +2720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2742,17 +2744,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="101.33203125" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="101.375" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2769,7 +2771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2786,7 +2788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2810,14 +2812,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="82.44140625" customWidth="1"/>
+    <col min="3" max="3" width="82.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2834,7 +2836,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2858,16 +2860,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.21875" customWidth="1"/>
-    <col min="3" max="3" width="151.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="151.125" customWidth="1"/>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2884,7 +2886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2901,7 +2903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2925,16 +2927,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
     <col min="3" max="3" width="89" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2951,7 +2953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2968,7 +2970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2992,17 +2994,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" customWidth="1"/>
-    <col min="3" max="3" width="72.33203125" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="3" max="3" width="72.375" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3019,7 +3021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3043,17 +3045,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="122.21875" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="122.25" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3070,7 +3072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3087,7 +3089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3104,7 +3106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3128,18 +3130,18 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="134.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="134.25" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3156,7 +3158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3173,7 +3175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3190,7 +3192,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAF8B00-BE49-442E-952E-D49E3191A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="15" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
     <sheet name="第二個說明對話" sheetId="2" r:id="rId2"/>
-    <sheet name="第二個說明對話_2" sheetId="13" r:id="rId3"/>
+    <sheet name="第二個說明對話_2" sheetId="35" r:id="rId3"/>
     <sheet name="第二個說明對話_3" sheetId="32" r:id="rId4"/>
     <sheet name="第二個說明對話_4" sheetId="20" r:id="rId5"/>
     <sheet name="第三個說明對話" sheetId="19" r:id="rId6"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="100">
   <si>
     <t>對話內容</t>
   </si>
@@ -125,10 +124,6 @@
   </si>
   <si>
     <t>把損壞核芯交給&lt;color=#AC0000&gt;開殼機&lt;/color&gt;後，它會自動幫你完成作業。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>這樣清楚多了，你得透過&lt;color=#AC0000&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -259,14 +254,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作檯&lt;/color&gt;上，這樣能看得更清楚。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在把注意力放回工作臺上的核芯，繼續剛才的修理流程。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>我們需要使用&lt;color=#AC0000&gt;處理器製作機&lt;/color&gt;──就是那隻看似&lt;color=#AC0000&gt;兔子&lt;/color&gt;的生物，你也可以這麼稱呼它，更簡短直觀一點。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -287,7 +274,174 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>──喔，你好像很在意&lt;color=#AC0000&gt;耐久值&lt;/color&gt;的問題？當然，&lt;color=#AC0000&gt;他們不會自己回復&lt;/color&gt;。</t>
+    <t>點擊與&lt;color=#AC0000&gt;壞掉處理器相同的形狀&lt;/color&gt;，製作出的成品才能進行替換。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以將事先做好的零件的物品放置在這裡，&lt;color=#AC0000&gt;左邊可放置原液，右邊可放置處理器零件&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外你應該也注意到了，&lt;color=#AC0000&gt;存放的位置是有限&lt;/color&gt;的。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果預先準備的&lt;color=#AC0000&gt;零件或試劑有錯&lt;/color&gt;，可以按下&lt;color=#AC0000&gt;回收按鈕&lt;/color&gt;，替你清出多的存放空間。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>謹記，我們現在的資源&lt;color=#AC0000&gt;只夠回收兩次錯誤物件&lt;/color&gt;，好好運用你的機會吧......</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將&lt;color=#AC0000&gt;新的處理器零件拖曳入核芯中替換&lt;/color&gt;，完成修復。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>話說你也注意到了吧，這次的核芯不是只有一處損壞，它的&lt;color=#AC0000&gt;電路板也燒毀了&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將電路板拿出，交給&lt;color=#AC0000&gt;電路修復台&lt;/color&gt;，但看你一副覺得拗口的樣子，可以同樣簡稱牠&lt;color=#AC0000&gt;螃蟹&lt;/color&gt;就好。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹與最開始講解的開殼機一樣，&lt;color=#AC0000&gt;只要你將物件交給它，就會自動完成任務&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>音檔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#AC0000&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>先把它拿進來，用&lt;color=#AC0000&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到出了什麼問題。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在得做個新的&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;的處理器。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>看見&lt;color=#AC0000&gt;兔耳朵上顯示的形狀&lt;/color&gt;了嗎？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一位客人來了，照方才我教你的流程走一遍，確認這個核芯是出了什麼問題。</t>
+  </si>
+  <si>
+    <t>機械進入&lt;color=#AC0000&gt;修理狀態，會隨時間逐步恢復耐久值，直到恢復至上限為止&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>音檔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>音檔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>插分圖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.mp3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬克西Maxi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>將&lt;color=#AC0000&gt;回復正常的電路板移入核芯內&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -295,185 +449,26 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>點擊與&lt;color=#AC0000&gt;壞掉處理器相同的形狀&lt;/color&gt;，製作出的成品才能進行替換。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以將事先做好的零件的物品放置在這裡，&lt;color=#AC0000&gt;左邊可放置原液，右邊可放置處理器零件&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>另外你應該也注意到了，&lt;color=#AC0000&gt;存放的位置是有限&lt;/color&gt;的。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果預先準備的&lt;color=#AC0000&gt;零件或試劑有錯&lt;/color&gt;，可以按下&lt;color=#AC0000&gt;回收按鈕&lt;/color&gt;，替你清出多的存放空間。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>謹記，我們現在的資源&lt;color=#AC0000&gt;只夠回收兩次錯誤物件&lt;/color&gt;，好好運用你的機會吧......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>將&lt;color=#AC0000&gt;新的處理器零件拖曳入核芯中替換&lt;/color&gt;，完成修復。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>話說你也注意到了吧，這次的核芯不是只有一處損壞，它的&lt;color=#AC0000&gt;電路板也燒毀了&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>將電路板拿出，交給&lt;color=#AC0000&gt;電路修復台&lt;/color&gt;，但看你一副覺得拗口的樣子，可以同樣簡稱牠&lt;color=#AC0000&gt;螃蟹&lt;/color&gt;就好。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>螃蟹與最開始講解的開殼機一樣，&lt;color=#AC0000&gt;只要你將物件交給它，就會自動完成任務&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>插分圖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>音檔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬克西Maxi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>我先教你一些基本的......首先，每位來訪的顧客會帶來他們的&lt;color=#AC0000&gt;損壞核芯&lt;/color&gt;，修好它是這間工作室存在的意義。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Customer.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>先把它拿進來，用&lt;color=#AC0000&gt;開殼機&lt;/color&gt;打開後，從內部構造才能看到出了什麼問題。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在得做個新的&lt;color=#AC0000&gt;形狀一樣&lt;/color&gt;的處理器。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>看見&lt;color=#AC0000&gt;兔耳朵上顯示的形狀&lt;/color&gt;了嗎？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬克西Maxi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬克西Maxi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一位客人來了，照方才我教你的流程走一遍，確認這個核芯是出了什麼問題。</t>
-  </si>
-  <si>
-    <t>機械進入&lt;color=#AC0000&gt;修理狀態，會隨時間逐步恢復耐久值，直到恢復至上限為止&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>拿起&lt;color=#AC0000&gt;修理工具&lt;/color&gt;，即可進行修復，當然不只是開殼機，&lt;color=#AC0000&gt;任何有耐久值的機器都可以用同樣的方法修復&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>插分圖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>音檔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>插分圖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>音檔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬克西Maxi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>插分圖</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.mp3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬克西Maxi</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>將&lt;color=#AC0000&gt;回復正常的電路板移入核芯內&lt;/color&gt;。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>.png</t>
+    <t>現在把核芯拿到&lt;color=#AC0000&gt;工作檯&lt;/color&gt;上，能夠看得更清楚內部需要更替的零件。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>而拿起&lt;color=#AC0000&gt;修理工具&lt;/color&gt;，即可修復耐久值，&lt;color=#AC0000&gt;有耐久值的機器都可用同樣的方法&lt;/color&gt;。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>好了，這樣就可以繼續剛才的修理流程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>清楚多了，你得透過&lt;color=#AC0000&gt;內部結構判斷該替換或修理哪種零件&lt;/color&gt;。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1453,19 +1448,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1474,44 +1469,44 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s">
         <v>67</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1522,17 +1517,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.75" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="4.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
     <col min="3" max="3" width="77" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1549,7 +1544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1557,7 +1552,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1566,7 +1561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1574,7 +1569,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1590,17 +1585,17 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1617,7 +1612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1625,7 +1620,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1634,7 +1629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1642,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1658,17 +1653,17 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="112.875" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="112.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1685,7 +1680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1693,7 +1688,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1702,7 +1697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1710,7 +1705,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1726,17 +1721,17 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1753,7 +1748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1761,7 +1756,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1770,7 +1765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1778,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1794,15 +1789,15 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="45.875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1819,7 +1814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1827,7 +1822,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1843,17 +1838,17 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="53.125" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
-    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="53.109375" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1870,7 +1865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1878,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1887,7 +1882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1895,7 +1890,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1911,15 +1906,15 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="119.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="119.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1936,7 +1931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1944,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1953,7 +1948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1961,7 +1956,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1970,7 +1965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1978,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1987,7 +1982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2011,15 +2006,15 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="47.5" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="47.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2036,7 +2031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2044,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -2053,7 +2048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2061,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2070,7 +2065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2078,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -2087,7 +2082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2095,7 +2090,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -2111,17 +2106,17 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="3" max="3" width="87.5" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="87.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2136,15 +2131,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -2160,15 +2155,15 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="60.75" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="60.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2185,7 +2180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2193,7 +2188,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -2202,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2210,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -2219,7 +2214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2227,7 +2222,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -2243,15 +2238,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="122.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2268,7 +2263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2285,7 +2280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2293,7 +2288,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2302,7 +2297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2310,7 +2305,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2327,15 +2322,15 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="57.375" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2352,7 +2347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2360,24 +2355,24 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2393,16 +2388,16 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
     <col min="3" max="3" width="82" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2419,7 +2414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2427,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -2443,17 +2438,17 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="144.5" customWidth="1"/>
-    <col min="4" max="4" width="41.625" customWidth="1"/>
+    <col min="3" max="3" width="144.44140625" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2462,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2476,44 +2471,44 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -2526,17 +2521,17 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="77.25" customWidth="1"/>
-    <col min="4" max="4" width="40.5" customWidth="1"/>
+    <col min="3" max="3" width="77.21875" customWidth="1"/>
+    <col min="4" max="4" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2545,44 +2540,44 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2592,15 +2587,15 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="92.875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="92.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2617,7 +2612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2625,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -2634,7 +2629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2642,7 +2637,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2658,18 +2653,18 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
     <col min="3" max="3" width="66" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2686,7 +2681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2694,7 +2689,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -2703,7 +2698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2711,7 +2706,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2720,7 +2715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2728,7 +2723,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2744,17 +2739,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="101.375" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2771,7 +2760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="226.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2779,29 +2768,12 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2812,14 +2784,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="82.5" customWidth="1"/>
+    <col min="3" max="3" width="82.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2830,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2844,10 +2816,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -2860,16 +2832,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="151.125" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="151.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2877,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -2886,7 +2858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2894,7 +2866,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
@@ -2903,7 +2875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2911,7 +2883,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -2927,16 +2899,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="89" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2953,7 +2925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2961,7 +2933,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -2970,7 +2942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2978,7 +2950,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2994,17 +2966,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="72.375" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="3" max="3" width="72.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3021,7 +2993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3029,7 +3001,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -3045,17 +3017,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.25" customWidth="1"/>
-    <col min="3" max="3" width="122.25" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="122.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3072,7 +3044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3089,7 +3061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3097,7 +3069,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -3106,7 +3078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3114,7 +3086,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -3130,18 +3102,18 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="13.25" customWidth="1"/>
-    <col min="3" max="3" width="134.25" customWidth="1"/>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="134.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3158,7 +3130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3166,7 +3138,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -3175,7 +3147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3183,30 +3155,30 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
